--- a/artfynd/A 46020-2025 artfynd.xlsx
+++ b/artfynd/A 46020-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>131078690</v>
       </c>
       <c r="B2" t="n">
-        <v>57076</v>
+        <v>57078</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -791,7 +791,7 @@
         <v>131078583</v>
       </c>
       <c r="B3" t="n">
-        <v>58043</v>
+        <v>58045</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 46020-2025 artfynd.xlsx
+++ b/artfynd/A 46020-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>131078690</v>
       </c>
       <c r="B2" t="n">
-        <v>57078</v>
+        <v>57079</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -791,7 +791,7 @@
         <v>131078583</v>
       </c>
       <c r="B3" t="n">
-        <v>58045</v>
+        <v>58046</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 46020-2025 artfynd.xlsx
+++ b/artfynd/A 46020-2025 artfynd.xlsx
@@ -791,7 +791,7 @@
         <v>131078583</v>
       </c>
       <c r="B3" t="n">
-        <v>58046</v>
+        <v>58047</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
